--- a/GBU_Riedl_Zuordnung.xlsx
+++ b/GBU_Riedl_Zuordnung.xlsx
@@ -518,7 +518,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Kataloge: riedl-mf-2026.1 (aus 81-20-mf-2026.9) und riedl-cyber-2026.1 (aus cyber-mf-2026.2)</t>
+          <t>Kataloge: riedl-mf-2026.2 (aus 81-20-mf-2026.10) und riedl-cyber-2026.2 (aus cyber-mf-2026.3)</t>
         </is>
       </c>
     </row>
@@ -528,7 +528,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Die Variante ersetzt die beiden Excel-Vorlagen (VFA „GBU Anlage leer" R 1.7.2 und „Vorlage GBU Cybersicherheit ab 04-26"). Sie ist ABGELEITET: jede Gefährdung, Frage, Regel und Maßnahme ist byteweise identisch mit dem MF- bzw. Cyber-Katalog; nur der Umfang ist kleiner. Umfang GBU: 202 Fragen, 63 Gefährdungen, 270 Regeln, 65 Karten (MF: 295/100/404/83). Umfang Cyber: 57 Fragen, 19 Gefährdungen, 114 Regeln (CY: 82/27/188).</t>
+          <t>Die Variante ersetzt die beiden Excel-Vorlagen (VFA „GBU Anlage leer" R 1.7.2 und „Vorlage GBU Cybersicherheit ab 04-26"). Sie ist ABGELEITET: jede Gefährdung, Frage, Regel und Maßnahme ist byteweise identisch mit dem MF- bzw. Cyber-Katalog; nur der Umfang ist kleiner. Umfang GBU: 209 Fragen, 63 Gefährdungen, 287 Regeln, 65 Karten (MF: 313/100/432/83). Umfang Cyber: 58 Fragen, 19 Gefährdungen, 116 Regeln (CY: 83/27/190).</t>
         </is>
       </c>
     </row>
@@ -729,7 +729,7 @@
         <is>
           <t>8.1 Notrufeinrichtung im Fahrkorb vorhanden? (TRIGGER, Karte K01 „Notrufeinrichtung im Fahrkorb")
 8.2 Art der Notrufeinrichtung (TRIGGER, Karte K01 „Notrufeinrichtung im Fahrkorb")
-8.3 Notruf auf eine rund um die Uhr besetzte Stelle aufgeschaltet? (TRIGGER, Karte K01 „Notrufeinrichtung im Fahrkorb")</t>
+8.3 Nachweis: Notruf auf eine rund um die Uhr besetzte Stelle aufgeschaltet (Aufschaltbestätigung, Testruf)? (TRIGGER, Karte K01 „Notrufeinrichtung im Fahrkorb")</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
@@ -902,7 +902,7 @@
 8.9b Ohne Fahrkorbtür: Lastenaufzug, der ausschließlich von eingewiesenen Personen benutzt wird (Einweisung dokumentiert)? (COMPENSATION, Karte A11 „Nutzerkreis")
 2.1 Nutzungsart der Anlage (MODIFIER, Einzelfrage)
 8.8 Schließkantensicherung der Fahrkorbtür (TRIGGER, Karte T08 „Schließkantensicherung der Fahrkorbtür / Schutz ohne Fahrkorbtür")
-8.7 Fahrkorbtür kraftbetätigt (automatisch)? (OPTIONAL, Einzelfrage)
+8.7 Fahrkorbtür kraftbetätigt (automatisch)? (TRIGGER, Karte T08 „Schließkantensicherung der Fahrkorbtür / Schutz ohne Fahrkorbtür")
 4.9 Nutzung durch Personen mit eingeschränkter Mobilität (Rollstuhl, Rollator, Sehbehinderung) zu erwarten? (MODIFIER, Karte A11 „Nutzerkreis")
 4.12 Nutzung durch unbeaufsichtigte Kinder zu erwarten (Schule, Kita, Wohnanlage)? (MODIFIER, Karte A11 „Nutzerkreis")</t>
         </is>
@@ -1079,7 +1079,7 @@
         <is>
           <t>8.10 Größte Stufenbildung / Haltegenauigkeit an den Haltestellen (TRIGGER, Karte K04 „Stufenbildung / Haltegenauigkeit")
 4.9 Nutzung durch Personen mit eingeschränkter Mobilität (Rollstuhl, Rollator, Sehbehinderung) zu erwarten? (MODIFIER, Karte A11 „Nutzerkreis")
-8.10m Stufenbildung gemessen [mm] (optional) (DOCUMENTATION, Karte K04 „Stufenbildung / Haltegenauigkeit")</t>
+8.10m Stufenbildung gemessen [mm] (DOCUMENTATION, Karte K04 „Stufenbildung / Haltegenauigkeit")</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -1383,7 +1383,7 @@
         <is>
           <t>8.12 Fahrkorbtürschürze (TRIGGER, Karte K05 „Fahrkorbtürschürze")
 8.13 Personenbefreiung ausschließlich durch fachkundige Personen (Betriebsanweisung, keine Selbstbefreiung durch Aufzugswärter)? (COMPENSATION, Karte K05 „Fahrkorbtürschürze")
-8.12m Schürzenlänge gemessen [mm] (optional) (DOCUMENTATION, Karte K05 „Fahrkorbtürschürze")</t>
+8.12m Schürzenlänge gemessen [mm] (DOCUMENTATION, Karte K05 „Fahrkorbtürschürze")</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1447,7 +1447,7 @@
 4.12 Nutzung durch unbeaufsichtigte Kinder zu erwarten (Schule, Kita, Wohnanlage)? (MODIFIER, Karte A11 „Nutzerkreis")
 8.15 Fahrkorbtür-Verriegelung (Fahrkorbtür außerhalb der Entriegelungszone verriegelt)? (COMPENSATION, Karte K06 „Abstand Fahrkorbschwelle – Schachtwand")
 8.15a Zusatzverriegelung an den Schachttüren vorhanden? (COMPENSATION, Karte K06 „Abstand Fahrkorbschwelle – Schachtwand")
-8.14m Abstand gemessen [mm] (optional) (DOCUMENTATION, Karte K06 „Abstand Fahrkorbschwelle – Schachtwand")</t>
+8.14m Abstand gemessen [mm] (DOCUMENTATION, Karte K06 „Abstand Fahrkorbschwelle – Schachtwand")</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
@@ -1501,8 +1501,9 @@
       <c r="G15" s="4" t="inlineStr">
         <is>
           <t>4.11 Fordert das Brandschutzkonzept des Gebäudes eine Brandfallsteuerung? (APPLICABILITY, Karte A14 „Gebäudeseitige Einrichtungen mit Schnittstelle zum Aufzug")
-8.21 Brandfallsteuerung vorhanden und in die Brandmeldeanlage eingebunden? (TRIGGER, Karte K11 „Brandfall: Steuerung und Hinweisschilder")
-8.21a Funktion der Brandfallsteuerung regelmäßig geprüft (Nachweis)? (TRIGGER, Karte K11 „Brandfall: Steuerung und Hinweisschilder")</t>
+8.21 Brandfallsteuerung vorhanden? (TRIGGER, Karte K11 „Brandfall: Steuerung und Hinweisschilder")
+8.21b Auslösung der Brandfallsteuerung (TRIGGER, Karte K11 „Brandfall: Steuerung und Hinweisschilder")
+8.21a Funktion der Brandfallsteuerung regelmäßig geprüft (Nachweis der Wartung/Prüfung der Aufzugsanlage)? (TRIGGER, Karte K11 „Brandfall: Steuerung und Hinweisschilder")</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1611,7 +1612,7 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Brandmeldeanlage, Brandfall- und Evakuierungssteuerung nicht abgestimmt</t>
+          <t>Brandmeldeanlage, Brandfall- und Evakuierungssteuerung nicht abgestimmt; Brandschutzeinrichtung behindert Betrieb oder Rettung</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
@@ -1619,7 +1620,7 @@
           <t>15.8 Brandmeldeanlage (BMA) im Gebäude vorhanden? (APPLICABILITY, Karte A14 „Gebäudeseitige Einrichtungen mit Schnittstelle zum Aufzug")
 15.8a Schnittstelle Brandmeldeanlage – Aufzug bekannt und abgestimmt (Brandfallsteuerung, Rückholung, Evakuierung)? (TRIGGER, Karte U06 „Brandschutzeinrichtungen des Gebäudes und ihre Schnittstellen zum Aufzug")
 15.8b Funktion der Schnittstelle BMA – Aufzug geprüft (Nachweis)? (TRIGGER, Karte U06 „Brandschutzeinrichtungen des Gebäudes und ihre Schnittstellen zum Aufzug")
-15.8c Evakuierungs-/Sonderfunktion des Aufzugs in dieser Gefährdungsbeurteilung berücksichtigt? (TRIGGER, Karte U06 „Brandschutzeinrichtungen des Gebäudes und ihre Schnittstellen zum Aufzug")
+15.8c Evakuierungs-/Sonderfunktion des Aufzugs im Brandschutzkonzept und in der Betriebsanweisung beschrieben (wer den Aufzug im Brandfall wie benutzen darf)? (TRIGGER, Karte U06 „Brandschutzeinrichtungen des Gebäudes und ihre Schnittstellen zum Aufzug")
 15.8d Behindert eine Brandschutzeinrichtung (Brandschutztür, Abschottung) den Aufzugsbetrieb oder die Personenrettung? (TRIGGER, Karte U06 „Brandschutzeinrichtungen des Gebäudes und ihre Schnittstellen zum Aufzug")</t>
         </is>
       </c>
@@ -1899,11 +1900,11 @@
           <t>4.1 Schachttüren mit Glas? (APPLICABILITY, Karte A09 „Glas an")
 4.3 Fahrkorbtüren mit Glas? (OPTIONAL, Karte A09 „Glas an")
 7.8 Glaseinsätze in Schacht-/Fahrkorbtüren aus normgerechtem Glas (Verbundsicherheitsglas nach EN 81-20 5.3.5.3)? (TRIGGER, Karte T04 „Glas in Schacht- und Fahrkorbtüren")
-7.9 Drahtglas (Gitterglas) verbaut? (TRIGGER, Karte T04 „Glas in Schacht- und Fahrkorbtüren")
+7.9 Ist das nicht normgerechte Glas ausschließlich Drahtglas (Gitterglas)? (TRIGGER, Karte T04 „Glas in Schacht- und Fahrkorbtüren")
 7.8a Glaseinsatz beschädigt, lose oder nicht sicher befestigt? (TRIGGER, Karte T04 „Glas in Schacht- und Fahrkorbtüren")
 7.9a Verglaste Türen als kraftbetätigte Schiebetüren ausgeführt? (TRIGGER, Karte T05 „Glas-Schiebetüren: Schutz gegen Einziehen von Kinderhänden")
-7.10 Schutz gegen Einziehen von Kinderhänden an Glas-Schiebetüren vorhanden (Sensorleiste, Abstand, Beschichtung)? (TRIGGER, Karte T05 „Glas-Schiebetüren: Schutz gegen Einziehen von Kinderhänden")
-4.12 Nutzung durch unbeaufsichtigte Kinder zu erwarten (Schule, Kita, Wohnanlage)? (MODIFIER, Karte A11 „Nutzerkreis")</t>
+7.9b Glasflächen in den kraftbetätigten Schiebetüren größer als ein Sichtfenster nach DIN EN 81-20 5.3.7.2.1 a) (Breite über 150 mm)? (TRIGGER, Karte T05 „Glas-Schiebetüren: Schutz gegen Einziehen von Kinderhänden")
+7.10 Schutz gegen Einziehen von Kinderhänden an Glas-Schiebetüren vorhanden (Sensorleiste, Abstand, Beschichtung)? (TRIGGER, Karte T05 „Glas-Schiebetüren: Schutz gegen Einziehen von Kinderhänden")</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
@@ -2018,7 +2019,7 @@
         <is>
           <t>3.6 Prüfplakette der ZÜS vorhanden und lesbar? (TRIGGER, Karte D04 „Wiederkehrende Prüfung (ZÜS)")
 3.8 Prüffrist der wiederkehrenden Prüfung (ZÜS) überschritten? (TRIGGER, Karte D04 „Wiederkehrende Prüfung (ZÜS)")
-3.7 Letzte ZÜS-Hauptprüfung: Prüfbericht liegt vor und ohne offene sicherheitsrelevante Mängel? (DOCUMENTATION, Karte D04 „Wiederkehrende Prüfung (ZÜS)")</t>
+3.7 Letzte ZÜS-Hauptprüfung: Prüfbericht liegt vor und ohne offene sicherheitsrelevante Mängel? (TRIGGER, Karte D04 „Wiederkehrende Prüfung (ZÜS)")</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
@@ -2195,7 +2196,7 @@
       <c r="G27" s="8" t="inlineStr">
         <is>
           <t>4.9 Nutzung durch Personen mit eingeschränkter Mobilität (Rollstuhl, Rollator, Sehbehinderung) zu erwarten? (APPLICABILITY, Karte A11 „Nutzerkreis")
-4.9a Barrierefreie Ausführung gefordert (Baugenehmigung, Nutzungskonzept, öffentlich zugängliches Gebäude)? (OPTIONAL, Karte A11 „Nutzerkreis")
+4.9a Barrierefreie Ausführung gefordert (Baugenehmigung, Nutzungskonzept, öffentlich zugängliches Gebäude)? (MODIFIER, Karte A11 „Nutzerkreis")
 8.22 Anlage nach DIN EN 81-70 barrierefrei ausgeführt? (TRIGGER, Karte K12 „Barrierefreie Ausführung")
 8.23 Bedienelemente in erreichbarer Höhe und ertastbar? (TRIGGER, Karte K12 „Barrierefreie Ausführung")
 8.24 Fahrkorbabmessungen für Rollstuhlnutzung ausreichend (mind. 1,00 m × 1,25 m, Fahrkorbtyp 1 nach DIN EN 81-70:2022-12)? (TRIGGER, Karte K12 „Barrierefreie Ausführung")</t>
@@ -2309,7 +2310,7 @@
         <is>
           <t>5.1 Beleuchtung an den Zuwegen zum Triebwerks-/Steuerungsraum vorhanden? (TRIGGER, Karte BZ1 „Beleuchtung der Zuwege zum Triebwerksraum")
 5.2 Beleuchtung an den Zuwegen ausreichend (mind. 50 Lux, funktionsfähig, Leuchten an geeigneter Stelle)? (TRIGGER, Karte BZ1 „Beleuchtung der Zuwege zum Triebwerksraum")
-5.2a Defekte Leuchten oder Leuchtkörper an den Zuwegen? (OPTIONAL, Karte BZ1 „Beleuchtung der Zuwege zum Triebwerksraum")</t>
+5.2a Defekte Leuchten oder Leuchtkörper an den Zuwegen? (TRIGGER, Karte BZ1 „Beleuchtung der Zuwege zum Triebwerksraum")</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -2367,7 +2368,8 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>5.5 Art des Aufstiegs zum Triebwerksraum (TRIGGER, Karte Z02 „Aufstieg zum Triebwerksraum")
+          <t>4.7 Eigener Triebwerks-/Maschinenraum vorhanden? (APPLICABILITY, Einzelfrage)
+5.5 Art des Aufstiegs zum Triebwerksraum (TRIGGER, Karte Z02 „Aufstieg zum Triebwerksraum")
 5.6 Bruch- oder Kippgefahr am Aufstieg (beschädigte Stufen, lose Leiter, fehlende Befestigung)? (TRIGGER, Karte Z02 „Aufstieg zum Triebwerksraum")</t>
         </is>
       </c>
@@ -2433,7 +2435,7 @@
         <is>
           <t>5.7 Führt der Zugang über eine Dachfläche, Dachkante, Empore oder eine andere Absturzkante? (TRIGGER, Karte Z03 „Absturzkanten und Überstiege auf dem Zugangsweg")
 5.7a Absturzkante durch Geländer oder Umwehrung dauerhaft gesichert? (COMPENSATION, Karte Z03 „Absturzkanten und Überstiege auf dem Zugangsweg")
-5.7b Verkehrsweg an der Absturzkante festgelegt und gekennzeichnet? (COMPENSATION, Karte Z03 „Absturzkanten und Überstiege auf dem Zugangsweg")
+5.7b Verkehrsweg an der Absturzkante festgelegt, gekennzeichnet und mit ausreichendem Sicherheitsabstand zur Absturzkante geführt (auf Dachflächen mindestens 2,00 m nach ASR A2.1)? (COMPENSATION, Karte Z03 „Absturzkanten und Überstiege auf dem Zugangsweg")
 5.8 Muss ein Treppenauge, eine Brüstung oder ein Fenster überstiegen werden? (TRIGGER, Karte Z03 „Absturzkanten und Überstiege auf dem Zugangsweg")</t>
         </is>
       </c>
@@ -2487,9 +2489,9 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>5.3 Sicherer, freier Verkehrsweg zum Triebwerks-/Steuerungsraum (trocken, sauber, ohne Stolperstellen, ohne Absturzkante)? (TRIGGER, Karte Z01 „Verkehrsweg zum Triebwerks-/Steuerungsraum")
-5.3a Verkehrsweg rutschig, glatt oder verschmutzt? (OPTIONAL, Karte Z01 „Verkehrsweg zum Triebwerks-/Steuerungsraum")
-5.3b Stolperstellen auf dem Verkehrsweg? (OPTIONAL, Karte Z01 „Verkehrsweg zum Triebwerks-/Steuerungsraum")
+          <t>5.3 Sicherer, freier Verkehrsweg zum Triebwerks-/Steuerungsraum (trocken, sauber, ohne Stolperstellen)? (TRIGGER, Karte Z01 „Verkehrsweg zum Triebwerks-/Steuerungsraum")
+5.3a Verkehrsweg rutschig, glatt oder verschmutzt? (TRIGGER, Karte Z01 „Verkehrsweg zum Triebwerks-/Steuerungsraum")
+5.3b Stolperstellen auf dem Verkehrsweg? (TRIGGER, Karte Z01 „Verkehrsweg zum Triebwerks-/Steuerungsraum")
 5.4 Enge oder niedrige Durchgänge (Breite &lt; 0,60 m oder Höhe &lt; 2,00 m)? (DOCUMENTATION, Karte Z01 „Verkehrsweg zum Triebwerks-/Steuerungsraum")</t>
         </is>
       </c>
@@ -2553,7 +2555,8 @@
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>5.9 Lässt sich der Zugangsbereich / Triebwerksraum jederzeit von innen verlassen? (TRIGGER, Karte Z06 „Zugangstür zum Triebwerks-/Maschinenraum")</t>
+          <t>4.7 Eigener Triebwerks-/Maschinenraum vorhanden? (APPLICABILITY, Einzelfrage)
+5.9 Lässt sich der Zugangsbereich / Triebwerksraum jederzeit von innen verlassen? (TRIGGER, Karte Z06 „Zugangstür zum Triebwerks-/Maschinenraum")</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
@@ -2601,16 +2604,17 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Fehlende oder unzureichende Zugangstür zum Triebwerks-/Maschinenraum</t>
+          <t>Fehlende oder unzureichende Zugangstür zum Triebwerks-/Maschinenraum bzw. nicht abschließbarer Steuerschrank</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>4.7 Eigener Triebwerks-/Maschinenraum vorhanden? (APPLICABILITY, Einzelfrage)
+          <t>4.7 Eigener Triebwerks-/Maschinenraum vorhanden? (MODIFIER, Einzelfrage)
 5.12 Zugangstür zum Triebwerks-/Maschinenraum vorhanden? (TRIGGER, Karte Z06 „Zugangstür zum Triebwerks-/Maschinenraum")
+5.14 Ohne Triebwerksraum: Steuerschrank (an der Haltestelle oder im Schacht) abschließbar, Zutritt nur für befugte Personen? (TRIGGER, Karte Z06 „Zugangstür zum Triebwerks-/Maschinenraum")
 5.12a Zugangstür abschließbar (Zutritt nur für befugte Personen)? (TRIGGER, Karte Z06 „Zugangstür zum Triebwerks-/Maschinenraum")
 5.12b Zugangstür unbeschädigt und leichtgängig? (TRIGGER, Karte Z06 „Zugangstür zum Triebwerks-/Maschinenraum")
-5.12c Durchgangsmaß der Zugangstür ausreichend (mind. 2,00 m hoch, 0,60 m breit)? (TRIGGER, Karte Z06 „Zugangstür zum Triebwerks-/Maschinenraum")</t>
+5.12c Durchgangsmaß der Zugangstür ausreichend (mind. 1,80 m hoch, 0,60 m breit)? (TRIGGER, Karte Z06 „Zugangstür zum Triebwerks-/Maschinenraum")</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2731,8 +2735,8 @@
 5.31 Offene Schalttafel ohne Schaltschrank vorhanden? (TRIGGER, Karte M01 „Elektrische Sicherheit im Triebwerks-/Maschinenraum")
 5.32 Offene Kontakte oder Schalter an Maschine, Kopierwerk oder Begrenzer? (TRIGGER, Karte M01 „Elektrische Sicherheit im Triebwerks-/Maschinenraum")
 5.33 Nicht berührungssichere Bauteile im Schaltschrank (bei geöffneter Tür erreichbar)? (TRIGGER, Karte M01 „Elektrische Sicherheit im Triebwerks-/Maschinenraum")
-5.34 Warnkennzeichnung für offene elektrische Kontakte vorhanden? (OPTIONAL, Karte M01 „Elektrische Sicherheit im Triebwerks-/Maschinenraum")
-5.35 Nachweis der elektrischen Prüfung nach DGUV Vorschrift 3 vorhanden (Prüfplakette / Protokoll aktuell)? (TRIGGER, Karte M02 „Prüfnachweise der elektrischen Anlage")</t>
+5.34 Warnkennzeichnung für offene elektrische Kontakte vorhanden? (TRIGGER, Karte M01 „Elektrische Sicherheit im Triebwerks-/Maschinenraum")
+5.35 Nachweis der elektrischen Prüfung der AUFZUGSANLAGE nach DGUV Vorschrift 3 vorhanden (Steuerung, Antrieb, Leitungen der Anlage; Prüfplakette / Protokoll aktuell)? (TRIGGER, Karte M02 „Prüfnachweise der elektrischen Anlage")</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -2796,7 +2800,7 @@
         <is>
           <t>5.38 Hauptpotenzialausgleich an der Aufzugskonstruktion vorhanden? (TRIGGER, Karte M01 „Elektrische Sicherheit im Triebwerks-/Maschinenraum")
 5.36 Bauseitige Elektroinstallation im Raum (Steckdosen, Schalter, Leitungen) unbeschädigt? (TRIGGER, Karte M01 „Elektrische Sicherheit im Triebwerks-/Maschinenraum")
-5.37 Prüfung der ortsfesten elektrischen Anlage nachgewiesen? (TRIGGER, Karte M02 „Prüfnachweise der elektrischen Anlage")</t>
+5.37 Prüfung der BAUSEITIGEN ortsfesten elektrischen Anlage des Raumes nachgewiesen (Zuleitung, Steckdosen, Raumbeleuchtung)? (TRIGGER, Karte M02 „Prüfnachweise der elektrischen Anlage")</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
@@ -3034,8 +3038,10 @@
         <is>
           <t>3.1 Aufzugsart (APPLICABILITY, Einzelfrage)
 6.10 Absperrventil am Hydraulikaggregat vorhanden? (TRIGGER, Karte M13 „Hydraulik: Absperrventil am Aggregat")
-6.10a Absperrventil gekennzeichnet und gut zugänglich? (TRIGGER, Karte M13 „Hydraulik: Absperrventil am Aggregat")
-6.11 Rohrbruchsicherungsventil vorhanden? (TRIGGER, Karte M12 „Hydraulik: Absinken des Fahrkorbs und Rohrbruchsicherung")
+6.10a Absperrventil gut zugänglich (ohne Hilfsmittel, ohne Umbauten erreichbar und bedienbar)? (TRIGGER, Karte M13 „Hydraulik: Absperrventil am Aggregat")
+6.10b Absperrventil dauerhaft gekennzeichnet (Funktion, Wirkrichtung)? (TRIGGER, Karte M13 „Hydraulik: Absperrventil am Aggregat")
+6.11 Rohrbruchsicherungsventil (Leitungsbruchventil) vorhanden? (TRIGGER, Karte M12 „Hydraulik: Absinken des Fahrkorbs und Rohrbruchsicherung")
+6.11a Zulässige Absturzsicherung statt Leitungsbruchventil (COMPENSATION, Karte M12 „Hydraulik: Absinken des Fahrkorbs und Rohrbruchsicherung")
 6.12 Einrichtung gegen Absinken (Kolbenabsinkverhinderung / Nachholsteuerung) vorhanden? (TRIGGER, Karte M12 „Hydraulik: Absinken des Fahrkorbs und Rohrbruchsicherung")
 6.13 Sinkt der Fahrkorb im Stillstand merklich ab? (TRIGGER, Karte M12 „Hydraulik: Absinken des Fahrkorbs und Rohrbruchsicherung")</t>
         </is>
@@ -3090,7 +3096,7 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>6.1 Antriebssystem / Regelung (APPLICABILITY, Einzelfrage)
+          <t>3.1 Aufzugsart (APPLICABILITY, Einzelfrage)
 6.4 Zwei unabhängige Fahrschütze / Abschaltwege vorhanden? (TRIGGER, Karte M10 „Schutzeinrichtungen der Steuerung (nach Unterlagen / Prüfbericht)")
 6.4a Bei nur einem Schütz: selbstüberwachende Steuerung mit Baumusterprüfung? (COMPENSATION, Karte M10 „Schutzeinrichtungen der Steuerung (nach Unterlagen / Prüfbericht)")</t>
         </is>
@@ -3269,7 +3275,8 @@
         <is>
           <t>5.53 Einrichtung für Notbetrieb / Personenbefreiung vorhanden (Handrad, Bremslüfthebel, Evakuierungseinheit, Notablass)? (TRIGGER, Karte M15 „Einrichtung für Notbetrieb / Personenbefreiung")
 5.53a Notbetriebseinrichtung gekennzeichnet (Fahrtrichtung, Bündigmarken)? (TRIGGER, Karte M15 „Einrichtung für Notbetrieb / Personenbefreiung")
-5.53b Beauftragte Personen in die Personenbefreiung eingewiesen? (TRIGGER, Karte D06 „Beauftragte Person (Aufzugswärter)")</t>
+5.53b Beauftragte Personen in die Personenbefreiung eingewiesen? (TRIGGER, Karte D06 „Beauftragte Person (Aufzugswärter)")
+E1 Beauftragte Person für die Aufzugsanlage (Aufzugswärter) schriftlich benannt? (MODIFIER, Karte D06 „Beauftragte Person (Aufzugswärter)")</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -3326,7 +3333,7 @@
 9.2 Geländer auf dem Fahrkorbdach vorhanden? (COMPENSATION, Karte F01a „Fahrkorbdach als Standfläche: Geländer, Fußleiste, Tragfähigkeit")
 9.3 Geländerhöhe auf dem Fahrkorbdach (COMPENSATION, Karte F01a „Fahrkorbdach als Standfläche: Geländer, Fußleiste, Tragfähigkeit")
 9.4 Fußleiste (mind. 100 mm) am Rand des Fahrkorbdachs vorhanden? (TRIGGER, Karte F01a „Fahrkorbdach als Standfläche: Geländer, Fußleiste, Tragfähigkeit")
-9.1m Abstand gemessen [mm] (optional) (DOCUMENTATION, Karte F01 „Abstand Fahrkorbdachkante – Schachtwand")</t>
+9.1m Abstand gemessen [mm] (DOCUMENTATION, Karte F01 „Abstand Fahrkorbdachkante – Schachtwand")</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -3864,7 +3871,8 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>10.13 Zugänge zum Schacht (Schachttüren, Inspektionstüren) und die zugehörigen Schalteinrichtungen frei und sicher begehbar? (TRIGGER, Karte S01 „Schachtumwehrung und Zugänge zum Schacht")</t>
+          <t>10.13 Zugänge zum Schacht (Schachttüren, Inspektionstüren) frei und sicher erreichbar (nicht zugestellt, nicht verbaut)? (TRIGGER, Karte S01 „Schachtumwehrung und Zugänge zum Schacht")
+10.13a Elektrische Sicherheitseinrichtungen der Schacht- und Inspektionstüren vorhanden und wirksam (Türkontakt im Sicherheitskreis)? (TRIGGER, Karte S01 „Schachtumwehrung und Zugänge zum Schacht")</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
@@ -4168,9 +4176,10 @@
       <c r="G60" s="7" t="inlineStr">
         <is>
           <t>11.10 Puffer für Fahrkorb und Gegengewicht vorhanden? (TRIGGER, Karte G03 „Puffer")
-11.10a Puffer unbeschädigt und nicht verschlissen? (TRIGGER, Karte G03 „Puffer")
+11.10a Zustand der Puffer (TRIGGER, Karte G03 „Puffer")
 11.10b Bauart der Puffer (TRIGGER, Karte G03 „Puffer")
-11.10c Ölstand hydraulischer Puffer prüfbar und Kennzeichnung vorhanden? (TRIGGER, Karte G03 „Puffer")
+11.10c Ölstand hydraulischer Puffer prüfbar (Schauglas, Peilstab oder gleichwertig)? (TRIGGER, Karte G03 „Puffer")
+11.10d Hydraulische Puffer gekennzeichnet (Typ, Füllmenge bzw. Ölsorte, zulässiger Ölstand)? (TRIGGER, Karte G03 „Puffer")
 3.1a Nenngeschwindigkeit [m/s] (MODIFIER, Einzelfrage)</t>
         </is>
       </c>
@@ -4400,9 +4409,9 @@
       <c r="G64" s="7" t="inlineStr">
         <is>
           <t>15.23 Unzulässige Temperaturen im Triebwerksraum oder Schacht möglich (Überhitzung über 40 °C, Frost)? (TRIGGER, Karte U04 „Umgebungsbedingungen")
-15.23a Feuchtigkeit oder Kondensat an sicherheitsrelevanten Bauteilen (Steuerung, Bremse, Türverriegelung)? (TRIGGER, Karte U04 „Umgebungsbedingungen")
+15.23a Feuchtigkeit oder Kondensat an sicherheitsrelevanten Bauteilen außerhalb der Schachtgrube (Steuerung, Bremse, Türverriegelung)? (TRIGGER, Karte U04 „Umgebungsbedingungen")
 15.23b Massive Korrosion, Betonabplatzungen oder andere bauliche Schäden am Schacht oder Triebwerksraum? (TRIGGER, Karte U04 „Umgebungsbedingungen")
-11.15 Wasser oder Feuchtigkeit in der Schachtgrube? (TRIGGER, Karte G07 „Wasser, Feuchtigkeit und wassergefährdende Stoffe in der Grube")
+11.15 Wasser oder Feuchtigkeit in der Schachtgrube (TRIGGER, Karte G07 „Wasser, Feuchtigkeit und wassergefährdende Stoffe in der Grube")
 11.16 Öl oder wassergefährdende Stoffe in der Grube ohne Auffangmöglichkeit? (TRIGGER, Karte G07 „Wasser, Feuchtigkeit und wassergefährdende Stoffe in der Grube")</t>
         </is>
       </c>
@@ -4564,14 +4573,14 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>1.3 Art der Aufzugssteuerung (APPLICABILITY, Einzelfrage)
-3.1.2 Höchste vorhandene Schnittstellenkategorie der Komponente „Aufzugssteuerung" (TRIGGER, Einzelfrage)
-3.1.3 Schutzmaßnahmen nach TRBS 1115-1 für „Aufzugssteuerung" (TRIGGER, Einzelfrage)
-3.1.4 Bleibt der Sicherheitskreis (Türkontakte, Endschalter, Fang-/Begrenzerkontakte) bei Manipulation der Steuerung durch eine unabhängige elektromechanische Kette wirksam? (COMPENSATION, Einzelfrage)
-2.1 Ist die Aufzugssteuerung (Steuerschrank, Bedien-/Serviceeinheit) für Unbefugte frei zugänglich? (MODIFIER, Einzelfrage)
-2.2 Ist der Triebwerks-/Maschinenraum für Unbefugte frei zugänglich? (MODIFIER, Einzelfrage)
-2.3 Ist der Aufzugsschacht für Unbefugte frei zugänglich (Grubenzugang, Schachttür ohne Notentriegelungsschutz, offene Wartungsklappe)? (MODIFIER, Einzelfrage)
-1.4 Triebwerks-/Maschinenraum vorhanden? (DOCUMENTATION, Einzelfrage)</t>
+          <t>1.3 Art der Aufzugssteuerung (APPLICABILITY, Karte CY-A „Systemabgrenzung der Anlage")
+3.1.2 Höchste vorhandene Schnittstellenkategorie der Komponente „Aufzugssteuerung" (TRIGGER, Karte CY-C1 „Komponente: Aufzugssteuerung")
+3.1.3 Schutzmaßnahmen nach TRBS 1115-1 für „Aufzugssteuerung" (TRIGGER, Karte CY-C1 „Komponente: Aufzugssteuerung")
+3.1.4 Bleibt der Sicherheitskreis (Türkontakte, Endschalter, Fang-/Begrenzerkontakte) bei Manipulation der Steuerung durch eine unabhängige elektromechanische Kette wirksam? (COMPENSATION, Karte CY-C1 „Komponente: Aufzugssteuerung")
+2.1 Ist die Aufzugssteuerung (Steuerschrank, Bedien-/Serviceeinheit) für Unbefugte frei zugänglich? (MODIFIER, Karte CY-Z „Zugang und Servicezugriff")
+2.2 Ist der Triebwerks-/Maschinenraum für Unbefugte frei zugänglich? (MODIFIER, Karte CY-Z „Zugang und Servicezugriff")
+2.3 Ist der Aufzugsschacht für Unbefugte frei zugänglich (Grubenzugang, Schachttür ohne Notentriegelungsschutz, offene Wartungsklappe)? (MODIFIER, Karte CY-Z „Zugang und Servicezugriff")
+1.4 Triebwerks-/Maschinenraum vorhanden? (DOCUMENTATION, Karte CY-A „Systemabgrenzung der Anlage")</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
@@ -4637,12 +4646,12 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>3.2.1 PESSRAL / programmierbare Sicherheitsschaltung vorhanden? (APPLICABILITY, Einzelfrage)
-3.2.2 Höchste vorhandene Schnittstellenkategorie der Komponente „PESSRAL (programmierbare Sicherheitsschaltung)" (TRIGGER, Einzelfrage)
-3.2.3 Schutzmaßnahmen nach TRBS 1115-1 für „PESSRAL (programmierbare Sicherheitsschaltung)" (TRIGGER, Einzelfrage)
-2.1 Ist die Aufzugssteuerung (Steuerschrank, Bedien-/Serviceeinheit) für Unbefugte frei zugänglich? (MODIFIER, Einzelfrage)
-2.2 Ist der Triebwerks-/Maschinenraum für Unbefugte frei zugänglich? (MODIFIER, Einzelfrage)
-2.3 Ist der Aufzugsschacht für Unbefugte frei zugänglich (Grubenzugang, Schachttür ohne Notentriegelungsschutz, offene Wartungsklappe)? (MODIFIER, Einzelfrage)</t>
+          <t>3.2.1 PESSRAL / programmierbare Sicherheitsschaltung vorhanden? (APPLICABILITY, Karte CY-C2 „Komponente: PESSRAL (programmierbare Sicherheitsschaltung)")
+3.2.2 Höchste vorhandene Schnittstellenkategorie der Komponente „PESSRAL (programmierbare Sicherheitsschaltung)" (TRIGGER, Karte CY-C2 „Komponente: PESSRAL (programmierbare Sicherheitsschaltung)")
+3.2.3 Schutzmaßnahmen nach TRBS 1115-1 für „PESSRAL (programmierbare Sicherheitsschaltung)" (TRIGGER, Karte CY-C2 „Komponente: PESSRAL (programmierbare Sicherheitsschaltung)")
+2.1 Ist die Aufzugssteuerung (Steuerschrank, Bedien-/Serviceeinheit) für Unbefugte frei zugänglich? (MODIFIER, Karte CY-Z „Zugang und Servicezugriff")
+2.2 Ist der Triebwerks-/Maschinenraum für Unbefugte frei zugänglich? (MODIFIER, Karte CY-Z „Zugang und Servicezugriff")
+2.3 Ist der Aufzugsschacht für Unbefugte frei zugänglich (Grubenzugang, Schachttür ohne Notentriegelungsschutz, offene Wartungsklappe)? (MODIFIER, Karte CY-Z „Zugang und Servicezugriff")</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -4707,13 +4716,13 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>3.3.1 Frequenzumrichter (geregelter Antrieb) vorhanden? (APPLICABILITY, Einzelfrage)
-3.3.2 Höchste vorhandene Schnittstellenkategorie der Komponente „Frequenzumrichter" (TRIGGER, Einzelfrage)
-3.3.3 Schutzmaßnahmen nach TRBS 1115-1 für „Frequenzumrichter" (TRIGGER, Einzelfrage)
-3.3.4 Wirkt bei Manipulation des Umrichters eine unabhängige Sicherheitskette (STO/sicher abgeschaltetes Moment, Bremse und Geschwindigkeitsbegrenzer unabhängig vom Umrichter)? (COMPENSATION, Einzelfrage)
-2.1 Ist die Aufzugssteuerung (Steuerschrank, Bedien-/Serviceeinheit) für Unbefugte frei zugänglich? (MODIFIER, Einzelfrage)
-2.2 Ist der Triebwerks-/Maschinenraum für Unbefugte frei zugänglich? (MODIFIER, Einzelfrage)
-2.3 Ist der Aufzugsschacht für Unbefugte frei zugänglich (Grubenzugang, Schachttür ohne Notentriegelungsschutz, offene Wartungsklappe)? (MODIFIER, Einzelfrage)</t>
+          <t>3.3.1 Frequenzumrichter (geregelter Antrieb) vorhanden? (APPLICABILITY, Karte CY-C3 „Komponente: Frequenzumrichter")
+3.3.2 Höchste vorhandene Schnittstellenkategorie der Komponente „Frequenzumrichter" (TRIGGER, Karte CY-C3 „Komponente: Frequenzumrichter")
+3.3.3 Schutzmaßnahmen nach TRBS 1115-1 für „Frequenzumrichter" (TRIGGER, Karte CY-C3 „Komponente: Frequenzumrichter")
+3.3.4 Wirkt bei Manipulation des Umrichters eine unabhängige Sicherheitskette (STO/sicher abgeschaltetes Moment, Bremse und Geschwindigkeitsbegrenzer unabhängig vom Umrichter)? (COMPENSATION, Karte CY-C3 „Komponente: Frequenzumrichter")
+2.1 Ist die Aufzugssteuerung (Steuerschrank, Bedien-/Serviceeinheit) für Unbefugte frei zugänglich? (MODIFIER, Karte CY-Z „Zugang und Servicezugriff")
+2.2 Ist der Triebwerks-/Maschinenraum für Unbefugte frei zugänglich? (MODIFIER, Karte CY-Z „Zugang und Servicezugriff")
+2.3 Ist der Aufzugsschacht für Unbefugte frei zugänglich (Grubenzugang, Schachttür ohne Notentriegelungsschutz, offene Wartungsklappe)? (MODIFIER, Karte CY-Z „Zugang und Servicezugriff")</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -4774,13 +4783,13 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>3.4.1 Notrufsystem mit digitaler Komponente (Mobilfunk/IP, programmierbares Notrufgerät) vorhanden? (APPLICABILITY, Einzelfrage)
-3.4.2 Höchste vorhandene Schnittstellenkategorie der Komponente „Notrufsystem (Zwei-Wege-Kommunikation)" (TRIGGER, Einzelfrage)
-3.4.3 Schutzmaßnahmen nach TRBS 1115-1 für „Notrufsystem (Zwei-Wege-Kommunikation)" (TRIGGER, Einzelfrage)
-3.4.4 Automatischer Testruf mit Ausfallmeldung an die Notrufzentrale (EN 81-28) vorhanden und wirksam? (COMPENSATION, Einzelfrage)
-2.1 Ist die Aufzugssteuerung (Steuerschrank, Bedien-/Serviceeinheit) für Unbefugte frei zugänglich? (MODIFIER, Einzelfrage)
-2.2 Ist der Triebwerks-/Maschinenraum für Unbefugte frei zugänglich? (MODIFIER, Einzelfrage)
-2.3 Ist der Aufzugsschacht für Unbefugte frei zugänglich (Grubenzugang, Schachttür ohne Notentriegelungsschutz, offene Wartungsklappe)? (MODIFIER, Einzelfrage)</t>
+          <t>3.4.1 Notrufsystem mit digitaler Komponente (Mobilfunk/IP, programmierbares Notrufgerät) vorhanden? (APPLICABILITY, Karte CY-C4 „Komponente: Notrufsystem (Zwei-Wege-Kommunikation)")
+3.4.2 Höchste vorhandene Schnittstellenkategorie der Komponente „Notrufsystem (Zwei-Wege-Kommunikation)" (TRIGGER, Karte CY-C4 „Komponente: Notrufsystem (Zwei-Wege-Kommunikation)")
+3.4.3 Schutzmaßnahmen nach TRBS 1115-1 für „Notrufsystem (Zwei-Wege-Kommunikation)" (TRIGGER, Karte CY-C4 „Komponente: Notrufsystem (Zwei-Wege-Kommunikation)")
+3.4.4 Automatischer Testruf mit Ausfallmeldung an die Notrufzentrale (EN 81-28) vorhanden und wirksam? (COMPENSATION, Karte CY-C4 „Komponente: Notrufsystem (Zwei-Wege-Kommunikation)")
+2.1 Ist die Aufzugssteuerung (Steuerschrank, Bedien-/Serviceeinheit) für Unbefugte frei zugänglich? (MODIFIER, Karte CY-Z „Zugang und Servicezugriff")
+2.2 Ist der Triebwerks-/Maschinenraum für Unbefugte frei zugänglich? (MODIFIER, Karte CY-Z „Zugang und Servicezugriff")
+2.3 Ist der Aufzugsschacht für Unbefugte frei zugänglich (Grubenzugang, Schachttür ohne Notentriegelungsschutz, offene Wartungsklappe)? (MODIFIER, Karte CY-Z „Zugang und Servicezugriff")</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -4845,13 +4854,13 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>3.6.1 Programmierbare Türsteuerung / Türantrieb mit Parametrierzugang vorhanden? (APPLICABILITY, Einzelfrage)
-3.6.2 Höchste vorhandene Schnittstellenkategorie der Komponente „Türsteuerung" (TRIGGER, Einzelfrage)
-3.6.3 Schutzmaßnahmen nach TRBS 1115-1 für „Türsteuerung" (TRIGGER, Einzelfrage)
-3.6.4 Wirkt die Schließkraftbegrenzung/Reversierung unabhängig von der programmierbaren Türsteuerung (mechanisch oder separates Gerät)? (COMPENSATION, Einzelfrage)
-2.1 Ist die Aufzugssteuerung (Steuerschrank, Bedien-/Serviceeinheit) für Unbefugte frei zugänglich? (MODIFIER, Einzelfrage)
-2.2 Ist der Triebwerks-/Maschinenraum für Unbefugte frei zugänglich? (MODIFIER, Einzelfrage)
-2.3 Ist der Aufzugsschacht für Unbefugte frei zugänglich (Grubenzugang, Schachttür ohne Notentriegelungsschutz, offene Wartungsklappe)? (MODIFIER, Einzelfrage)</t>
+          <t>3.6.1 Programmierbare Türsteuerung / Türantrieb mit Parametrierzugang vorhanden? (APPLICABILITY, Karte CY-C6 „Komponente: Türsteuerung")
+3.6.2 Höchste vorhandene Schnittstellenkategorie der Komponente „Türsteuerung" (TRIGGER, Karte CY-C6 „Komponente: Türsteuerung")
+3.6.3 Schutzmaßnahmen nach TRBS 1115-1 für „Türsteuerung" (TRIGGER, Karte CY-C6 „Komponente: Türsteuerung")
+3.6.4 Wirkt die Schließkraftbegrenzung/Reversierung unabhängig von der programmierbaren Türsteuerung (mechanisch oder separates Gerät)? (COMPENSATION, Karte CY-C6 „Komponente: Türsteuerung")
+2.1 Ist die Aufzugssteuerung (Steuerschrank, Bedien-/Serviceeinheit) für Unbefugte frei zugänglich? (MODIFIER, Karte CY-Z „Zugang und Servicezugriff")
+2.2 Ist der Triebwerks-/Maschinenraum für Unbefugte frei zugänglich? (MODIFIER, Karte CY-Z „Zugang und Servicezugriff")
+2.3 Ist der Aufzugsschacht für Unbefugte frei zugänglich (Grubenzugang, Schachttür ohne Notentriegelungsschutz, offene Wartungsklappe)? (MODIFIER, Karte CY-Z „Zugang und Servicezugriff")</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -4912,9 +4921,9 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>1.6 Anbindung an bauseitige Systeme vorhanden (Brandmeldeanlage/Brandfallsteuerung, Entrauchung, Gebäudeleittechnik, Zutrittssystem)? (APPLICABILITY, Einzelfrage)
-3.14.1 Ist die Schnittstelle zu den bauseitigen Systemen rückwirkungsfrei (definierte Signale/potenzialfreie Kontakte; bauseitige Signale können Sicherheitsfunktionen des Aufzugs nicht außer Kraft setzen)? (TRIGGER, Einzelfrage)
-3.14.2 Nimmt der Aufzug bei Ausfall oder Manipulation des bauseitigen Signals (z. B. Brandfallsteuerung) einen sicheren Zustand ein (Brandfallfahrt in die Evakuierungshaltestelle, kein Weiterbetrieb)? (TRIGGER, Einzelfrage)</t>
+          <t>1.6 Anbindung an bauseitige Systeme vorhanden (Brandmeldeanlage/Brandfallsteuerung, Entrauchung, Gebäudeleittechnik, Zutrittssystem)? (APPLICABILITY, Karte CY-A „Systemabgrenzung der Anlage")
+3.14.1 Ist die Schnittstelle zu den bauseitigen Systemen rückwirkungsfrei (definierte Signale/potenzialfreie Kontakte; bauseitige Signale können Sicherheitsfunktionen des Aufzugs nicht außer Kraft setzen)? (TRIGGER, Karte CY-G „Bauseitige Einrichtungen (Brandfallsteuerung, Entrauchung, Zutritt)")
+3.14.2 Nimmt der Aufzug bei Ausfall oder Manipulation des bauseitigen Signals (z. B. Brandfallsteuerung) einen sicheren Zustand ein (Brandfallfahrt in die Evakuierungshaltestelle, kein Weiterbetrieb)? (TRIGGER, Karte CY-G „Bauseitige Einrichtungen (Brandfallsteuerung, Entrauchung, Zutritt)")</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -4977,8 +4986,8 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2.1 Ist die Aufzugssteuerung (Steuerschrank, Bedien-/Serviceeinheit) für Unbefugte frei zugänglich? (TRIGGER, Einzelfrage)
-2.4 Sind die Service- und Programmierschnittstellen (Serviceanschluss, USB, Speicherkarte, Diagnosestecker) gegen unbefugte Nutzung gesichert (verschlossene Abdeckung, Freigabe nur mit Schlüssel/Code)? (TRIGGER, Einzelfrage)</t>
+          <t>2.1 Ist die Aufzugssteuerung (Steuerschrank, Bedien-/Serviceeinheit) für Unbefugte frei zugänglich? (TRIGGER, Karte CY-Z „Zugang und Servicezugriff")
+2.4 Sind die Service- und Programmierschnittstellen (Serviceanschluss, USB, Speicherkarte, Diagnosestecker) gegen unbefugte Nutzung gesichert (verschlossene Abdeckung, Freigabe nur mit Schlüssel/Code)? (TRIGGER, Karte CY-Z „Zugang und Servicezugriff")</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -5043,9 +5052,10 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2.5 Werden Standard-/Werkszugangsdaten (Passwörter, PINs, Servicecodes) verwendet oder sind die Zugangsdaten nicht bekannt? (TRIGGER, Einzelfrage)
-2.6 Sind Zugriffsrechte rollenbasiert vergeben (Betreiber, Wartungsfirma, Hersteller) und werden sie bei Personal- oder Firmenwechsel entzogen? (TRIGGER, Einzelfrage)
-1.5 Anlage mit Netzwerk- oder Internetanbindung (Fernüberwachung, Fernwartung, Gateway/Router/Modem, Gebäudeleittechnik)? (MODIFIER, Einzelfrage)</t>
+          <t>2.5 Werden Standard-/Werkszugangsdaten (Passwörter, PINs, Servicecodes) verwendet? (TRIGGER, Karte CY-Z „Zugang und Servicezugriff")
+2.5a Sind dem Betreiber die Zugangsdaten der Anlage bekannt und liegen sie gesichert vor (Übergabe durch Hersteller/Wartungsfirma dokumentiert)? (TRIGGER, Karte CY-Z „Zugang und Servicezugriff")
+2.6 Sind Zugriffsrechte rollenbasiert vergeben (Betreiber, Wartungsfirma, Hersteller) und werden sie bei Personal- oder Firmenwechsel entzogen? (TRIGGER, Karte CY-Z „Zugang und Servicezugriff")
+1.5 Anlage mit Netzwerk- oder Internetanbindung (Fernüberwachung, Fernwartung, Gateway/Router/Modem, Gebäudeleittechnik)? (MODIFIER, Karte CY-A „Systemabgrenzung der Anlage")</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
@@ -5099,7 +5109,7 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>2.7 Ist geregelt, welche Servicegeräte, Laptops und Wechseldatenträger an die Anlage angeschlossen werden dürfen (nur freigegebene, geprüfte Geräte; kein privater Datenträger)? (TRIGGER, Einzelfrage)</t>
+          <t>2.7 Ist geregelt, welche Servicegeräte, Laptops und Wechseldatenträger an die Anlage angeschlossen werden dürfen (nur freigegebene, geprüfte Geräte; kein privater Datenträger)? (TRIGGER, Karte CY-Z „Zugang und Servicezugriff")</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
@@ -5153,12 +5163,12 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>1.5 Anlage mit Netzwerk- oder Internetanbindung (Fernüberwachung, Fernwartung, Gateway/Router/Modem, Gebäudeleittechnik)? (APPLICABILITY, Einzelfrage)
-3.11.1 Fernüberwachung (Zustandsmeldung, Störungsmeldung an Leitstelle/Hersteller) vorhanden? (APPLICABILITY, Einzelfrage)
-3.11.2 Ist die Fernüberwachung ausschließlich lesend (kein Schreib-, Steuer- oder Parametrierzugriff über diesen Kanal)? (TRIGGER, Einzelfrage)
-4.1 Ist das Aufzugsnetz vom Gebäude-/Büronetz und vom Internet getrennt (eigenes Segment, Firewall, keine direkte Erreichbarkeit der Steuerung von außen)? (TRIGGER, Einzelfrage)
-4.3 Ist der Fernzugriff individuell authentifiziert (personenbezogene Zugänge, Zwei-Faktor oder gleichwertig) und verschlüsselt? (TRIGGER, Einzelfrage)
-4.4 Werden Zugriffe auf die Anlage (vor Ort über Servicegeräte und per Fernzugriff) protokolliert und die Protokolle ausgewertet? (TRIGGER, Einzelfrage)</t>
+          <t>1.5 Anlage mit Netzwerk- oder Internetanbindung (Fernüberwachung, Fernwartung, Gateway/Router/Modem, Gebäudeleittechnik)? (APPLICABILITY, Karte CY-A „Systemabgrenzung der Anlage")
+3.11.1 Fernüberwachung (Zustandsmeldung, Störungsmeldung an Leitstelle/Hersteller) vorhanden? (APPLICABILITY, Karte CY-N „Netz, Fernzugriff, Gateway und Härtung")
+3.11.2 Ist die Fernüberwachung ausschließlich lesend (kein Schreib-, Steuer- oder Parametrierzugriff über diesen Kanal)? (TRIGGER, Karte CY-N „Netz, Fernzugriff, Gateway und Härtung")
+4.1 Ist das Aufzugsnetz vom Gebäude-/Büronetz und vom Internet getrennt (eigenes Segment, Firewall, keine direkte Erreichbarkeit der Steuerung von außen)? (TRIGGER, Karte CY-N „Netz, Fernzugriff, Gateway und Härtung")
+4.3 Ist der Fernzugriff individuell authentifiziert (personenbezogene Zugänge, Zwei-Faktor oder gleichwertig) und verschlüsselt? (TRIGGER, Karte CY-N „Netz, Fernzugriff, Gateway und Härtung")
+4.4 Werden Zugriffe auf die Anlage (vor Ort über Servicegeräte und per Fernzugriff) protokolliert und die Protokolle ausgewertet? (TRIGGER, Karte CY-N „Netz, Fernzugriff, Gateway und Härtung")</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -5217,12 +5227,12 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>1.5 Anlage mit Netzwerk- oder Internetanbindung (Fernüberwachung, Fernwartung, Gateway/Router/Modem, Gebäudeleittechnik)? (APPLICABILITY, Einzelfrage)
-3.12.1 Remote-Service / Fernwartung (Hersteller-Fernzugriff, Service-App, VPN) vorhanden? (APPLICABILITY, Einzelfrage)
-4.1 Ist das Aufzugsnetz vom Gebäude-/Büronetz und vom Internet getrennt (eigenes Segment, Firewall, keine direkte Erreichbarkeit der Steuerung von außen)? (TRIGGER, Einzelfrage)
-4.2 Wird ein Fernzugriff nur nach Freigabe durch den Betreiber und nur für die Dauer des Bedarfs aktiviert? (TRIGGER, Einzelfrage)
-4.3 Ist der Fernzugriff individuell authentifiziert (personenbezogene Zugänge, Zwei-Faktor oder gleichwertig) und verschlüsselt? (TRIGGER, Einzelfrage)
-4.4 Werden Zugriffe auf die Anlage (vor Ort über Servicegeräte und per Fernzugriff) protokolliert und die Protokolle ausgewertet? (TRIGGER, Einzelfrage)</t>
+          <t>1.5 Anlage mit Netzwerk- oder Internetanbindung (Fernüberwachung, Fernwartung, Gateway/Router/Modem, Gebäudeleittechnik)? (APPLICABILITY, Karte CY-A „Systemabgrenzung der Anlage")
+3.12.1 Remote-Service / Fernwartung (Hersteller-Fernzugriff, Service-App, VPN) vorhanden? (APPLICABILITY, Karte CY-N „Netz, Fernzugriff, Gateway und Härtung")
+4.1 Ist das Aufzugsnetz vom Gebäude-/Büronetz und vom Internet getrennt (eigenes Segment, Firewall, keine direkte Erreichbarkeit der Steuerung von außen)? (TRIGGER, Karte CY-N „Netz, Fernzugriff, Gateway und Härtung")
+4.2 Wird ein Fernzugriff nur nach Freigabe durch den Betreiber und nur für die Dauer des Bedarfs aktiviert? (TRIGGER, Karte CY-N „Netz, Fernzugriff, Gateway und Härtung")
+4.3 Ist der Fernzugriff individuell authentifiziert (personenbezogene Zugänge, Zwei-Faktor oder gleichwertig) und verschlüsselt? (TRIGGER, Karte CY-N „Netz, Fernzugriff, Gateway und Härtung")
+4.4 Werden Zugriffe auf die Anlage (vor Ort über Servicegeräte und per Fernzugriff) protokolliert und die Protokolle ausgewertet? (TRIGGER, Karte CY-N „Netz, Fernzugriff, Gateway und Härtung")</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
@@ -5276,11 +5286,11 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>1.5 Anlage mit Netzwerk- oder Internetanbindung (Fernüberwachung, Fernwartung, Gateway/Router/Modem, Gebäudeleittechnik)? (APPLICABILITY, Einzelfrage)
-3.13.1 Gateway / Router / Modem / WLAN- oder Service-Dongle an der Anlage vorhanden? (APPLICABILITY, Einzelfrage)
-3.13.2 Ist das Gateway mit Firewall/Netztrennung zur Aufzugssteuerung konfiguriert und sind nur benötigte Ports und Dienste freigegeben? (TRIGGER, Einzelfrage)
-3.13.3 Sind die Werkszugangsdaten des Gateways/Routers geändert und ist die Administration nur für Berechtigte erreichbar? (TRIGGER, Einzelfrage)
-3.13.4 Ist die Firmware des Gateways aktuell und ein Update-Verfahren geregelt? (TRIGGER, Einzelfrage)</t>
+          <t>1.5 Anlage mit Netzwerk- oder Internetanbindung (Fernüberwachung, Fernwartung, Gateway/Router/Modem, Gebäudeleittechnik)? (APPLICABILITY, Karte CY-A „Systemabgrenzung der Anlage")
+3.13.1 Gateway / Router / Modem / WLAN- oder Service-Dongle an der Anlage vorhanden? (APPLICABILITY, Karte CY-N „Netz, Fernzugriff, Gateway und Härtung")
+3.13.2 Ist das Gateway mit Firewall/Netztrennung zur Aufzugssteuerung konfiguriert und sind nur benötigte Ports und Dienste freigegeben? (TRIGGER, Karte CY-N „Netz, Fernzugriff, Gateway und Härtung")
+3.13.3 Sind die Werkszugangsdaten des Gateways/Routers geändert und ist die Administration nur für Berechtigte erreichbar? (TRIGGER, Karte CY-N „Netz, Fernzugriff, Gateway und Härtung")
+3.13.4 Ist die Firmware des Gateways aktuell und ein Update-Verfahren geregelt? (TRIGGER, Karte CY-N „Netz, Fernzugriff, Gateway und Härtung")</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
@@ -5334,8 +5344,8 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>4.5 Software-/Firmwarestand und bekannte Schwachstellen (TRIGGER, Einzelfrage)
-1.5 Anlage mit Netzwerk- oder Internetanbindung (Fernüberwachung, Fernwartung, Gateway/Router/Modem, Gebäudeleittechnik)? (MODIFIER, Einzelfrage)</t>
+          <t>4.5 Software-/Firmwarestand und bekannte Schwachstellen (TRIGGER, Karte CY-N „Netz, Fernzugriff, Gateway und Härtung")
+1.5 Anlage mit Netzwerk- oder Internetanbindung (Fernüberwachung, Fernwartung, Gateway/Router/Modem, Gebäudeleittechnik)? (MODIFIER, Karte CY-A „Systemabgrenzung der Anlage")</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
@@ -5389,8 +5399,8 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>4.6 Sind nicht benötigte Funktionen, Ports, Dienste und Schnittstellen deaktiviert (Funktionsreduzierung)? (TRIGGER, Einzelfrage)
-1.5 Anlage mit Netzwerk- oder Internetanbindung (Fernüberwachung, Fernwartung, Gateway/Router/Modem, Gebäudeleittechnik)? (MODIFIER, Einzelfrage)</t>
+          <t>4.6 Sind nicht benötigte Funktionen, Ports, Dienste und Schnittstellen deaktiviert (Funktionsreduzierung)? (TRIGGER, Karte CY-N „Netz, Fernzugriff, Gateway und Härtung")
+1.5 Anlage mit Netzwerk- oder Internetanbindung (Fernüberwachung, Fernwartung, Gateway/Router/Modem, Gebäudeleittechnik)? (MODIFIER, Karte CY-A „Systemabgrenzung der Anlage")</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
@@ -5444,7 +5454,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>1.7 Vorgaben des Herstellers zur Cybersicherheit (TRIGGER, Einzelfrage)</t>
+          <t>1.7 Vorgaben des Herstellers zur Cybersicherheit (TRIGGER, Karte CY-A „Systemabgrenzung der Anlage")</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -5503,7 +5513,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>5.8 Ist sichergestellt, dass die Cyber-Schutzmaßnahmen die Sicherheitsfunktionen der Anlage nicht negativ beeinflussen (Rückwirkungsfreiheit, z. B. keine Abschaltung des Notrufs durch die Firewall)? (TRIGGER, Einzelfrage)</t>
+          <t>5.8 Ist sichergestellt, dass die Cyber-Schutzmaßnahmen die Sicherheitsfunktionen der Anlage nicht negativ beeinflussen (Rückwirkungsfreiheit, z. B. keine Abschaltung des Notrufs durch die Firewall)? (TRIGGER, Karte CY-O „Organisation, Fachkunde und Notfallmanagement")</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
@@ -5557,13 +5567,13 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>5.5 Sind Art, Umfang und Fristen der Überprüfung und Kontrolle der Cyber-Schutzmaßnahmen schriftlich festgelegt? (TRIGGER, Einzelfrage)
-5.6 Liegt ein Nachweis der Wirksamkeit der Cyber-Schutzmaßnahmen vor (TRBS 1115-1 Abschnitt 5)? (TRIGGER, Einzelfrage)
-5.7 Liegt eine Bestätigung der Funktionsfähigkeit der Cyber-Schutzmaßnahmen vor (TRBS 1115-1 Abschnitt 8.2)? (TRIGGER, Einzelfrage)
-5.11 Wurden Cyberbedrohungen gemäß TRBS 1115 Teil 1 bei der Gefährdungsbeurteilung der Anlage berücksichtigt (diese Cyber-GBU vollständig bearbeitet und in die Gesamt-GBU übernommen)? (DOCUMENTATION, Einzelfrage)
-5.12 Sind alle sicherheitsrelevanten MSR-Einrichtungen und weiteren schutzbedürftigen Einrichtungen erfasst und dokumentiert (Komponentenliste vollständig, weitere Komponenten als Freitext ergänzt)? (DOCUMENTATION, Einzelfrage)
-5.13 Wurde bei der Festlegung der Maßnahmen berücksichtigt, dass bei überwachungsbedürftigen Anlagen nach ÜAnlG stets von einem erheblichen Risiko für Sicherheit und Gesundheit auszugehen ist? (DOCUMENTATION, Einzelfrage)
-5.14 Wurde der Stand der Technik herangezogen (TRBS 1115 Teil 1, EK-ZÜS B-002/BA-017, Herstellervorgaben, aktuelle Schwachstellenhinweise)? (DOCUMENTATION, Einzelfrage)</t>
+          <t>5.5 Sind Art, Umfang und Fristen der Überprüfung und Kontrolle der Cyber-Schutzmaßnahmen schriftlich festgelegt? (TRIGGER, Karte CY-O „Organisation, Fachkunde und Notfallmanagement")
+5.6 Liegt ein Nachweis der Wirksamkeit der Cyber-Schutzmaßnahmen vor (TRBS 1115-1 Abschnitt 5)? (TRIGGER, Karte CY-D „Nachweise für den ZÜS-Abschlusscheck")
+5.7 Liegt eine Bestätigung der Funktionsfähigkeit der Cyber-Schutzmaßnahmen vor (TRBS 1115-1 Abschnitt 8.2)? (TRIGGER, Karte CY-D „Nachweise für den ZÜS-Abschlusscheck")
+5.11 Wurden Cyberbedrohungen gemäß TRBS 1115 Teil 1 bei der Gefährdungsbeurteilung der Anlage berücksichtigt (diese Cyber-GBU vollständig bearbeitet und in die Gesamt-GBU übernommen)? (DOCUMENTATION, Karte CY-D „Nachweise für den ZÜS-Abschlusscheck")
+5.12 Sind alle sicherheitsrelevanten MSR-Einrichtungen und weiteren schutzbedürftigen Einrichtungen erfasst und dokumentiert (Komponentenliste vollständig, weitere Komponenten als Freitext ergänzt)? (DOCUMENTATION, Karte CY-D „Nachweise für den ZÜS-Abschlusscheck")
+5.13 Wurde bei der Festlegung der Maßnahmen berücksichtigt, dass bei überwachungsbedürftigen Anlagen nach ÜAnlG stets von einem erheblichen Risiko für Sicherheit und Gesundheit auszugehen ist? (DOCUMENTATION, Karte CY-D „Nachweise für den ZÜS-Abschlusscheck")
+5.14 Wurde der Stand der Technik herangezogen (TRBS 1115 Teil 1, EK-ZÜS B-002/BA-017, Herstellervorgaben, aktuelle Schwachstellenhinweise)? (DOCUMENTATION, Karte CY-D „Nachweise für den ZÜS-Abschlusscheck")</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
@@ -5617,8 +5627,8 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>5.10 Wurden nach Aussage des Betreibers prüfpflichtige Änderungen mit Einfluss auf die Cybersicherheit durchgeführt (Steuerungstausch, neue Fernanbindung, Software-Update sicherheitsrelevanter Komponenten)? (TRIGGER, Einzelfrage)
-5.10a Wurden diese Änderungen geprüft (ZÜS-Prüfung nach prüfpflichtiger Änderung) und in der Gefährdungsbeurteilung nachgezogen? (TRIGGER, Einzelfrage)</t>
+          <t>5.10 Wurden nach Aussage des Betreibers prüfpflichtige Änderungen mit Einfluss auf die Cybersicherheit durchgeführt (Steuerungstausch, neue Fernanbindung, Software-Update sicherheitsrelevanter Komponenten)? (TRIGGER, Karte CY-O „Organisation, Fachkunde und Notfallmanagement")
+5.10a Wurden diese Änderungen geprüft (ZÜS-Prüfung nach prüfpflichtiger Änderung) und in der Gefährdungsbeurteilung nachgezogen? (TRIGGER, Karte CY-O „Organisation, Fachkunde und Notfallmanagement")</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
@@ -5672,7 +5682,7 @@
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>5.9 Werden neue Erkenntnisse zur Cybersicherheit (Herstellerhinweise, Schwachstellenmeldungen, CERT-Warnungen) in die Gefährdungsbeurteilung eingebunden? (TRIGGER, Einzelfrage)</t>
+          <t>5.9 Werden neue Erkenntnisse zur Cybersicherheit (Herstellerhinweise, Schwachstellenmeldungen, CERT-Warnungen) in die Gefährdungsbeurteilung eingebunden? (TRIGGER, Karte CY-O „Organisation, Fachkunde und Notfallmanagement")</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
@@ -6428,7 +6438,7 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
@@ -6484,7 +6494,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
@@ -6540,7 +6550,7 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
@@ -6624,7 +6634,7 @@
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
@@ -6736,7 +6746,7 @@
         </is>
       </c>
       <c r="D36" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
@@ -7367,7 +7377,7 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D5" s="2" t="inlineStr"/>
     </row>
@@ -7378,10 +7388,10 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D6" s="2" t="inlineStr"/>
     </row>
@@ -7392,10 +7402,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D7" s="2" t="inlineStr"/>
     </row>
@@ -7420,10 +7430,10 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D9" s="2" t="inlineStr"/>
     </row>
@@ -7434,10 +7444,10 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D10" s="2" t="inlineStr"/>
     </row>
@@ -7448,10 +7458,10 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11" s="2" t="inlineStr"/>
     </row>
@@ -7462,10 +7472,10 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D12" s="2" t="inlineStr"/>
     </row>
@@ -7490,10 +7500,10 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="D14" s="2" t="inlineStr"/>
     </row>
@@ -7518,10 +7528,10 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>404</v>
+        <v>432</v>
       </c>
       <c r="D16" s="2" t="inlineStr"/>
     </row>
@@ -7546,10 +7556,10 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D18" s="2" t="inlineStr"/>
     </row>
@@ -7560,10 +7570,10 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D19" s="2" t="inlineStr"/>
     </row>
@@ -7655,10 +7665,10 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D27" s="2" t="inlineStr"/>
     </row>
@@ -7669,10 +7679,10 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D28" s="2" t="inlineStr"/>
     </row>
@@ -7697,10 +7707,10 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D30" s="2" t="inlineStr"/>
     </row>
@@ -7741,17 +7751,17 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>128 / 189</t>
+          <t>127 / 188</t>
         </is>
       </c>
     </row>
@@ -7763,17 +7773,17 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>136 / 184</t>
+          <t>132 / 180</t>
         </is>
       </c>
     </row>
@@ -7795,7 +7805,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>119 / 177</t>
+          <t>118 / 176</t>
         </is>
       </c>
     </row>
